--- a/results_coherence.xlsx
+++ b/results_coherence.xlsx
@@ -1,37 +1,192 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_74212A8AD049320F62355476585DCE3A874707F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D3344F0-687C-4C96-B917-91E0BCD7F7C8}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="48">
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Best Parameters</t>
+  </si>
+  <si>
+    <t>CV Balanced Accuracy</t>
+  </si>
+  <si>
+    <t>Test Balanced Accuracy</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>SVM</t>
+  </si>
+  <si>
+    <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'linear'}</t>
+  </si>
+  <si>
+    <t>{'svm__C': 10, 'svm__gamma': 'scale', 'svm__kernel': 'rbf'}</t>
+  </si>
+  <si>
+    <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'rbf'}</t>
+  </si>
+  <si>
+    <t>MEAN</t>
+  </si>
+  <si>
+    <t>STD</t>
+  </si>
+  <si>
+    <t>0.6288</t>
+  </si>
+  <si>
+    <t>0.1590</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 5, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 5, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 5, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 10, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 10, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 5, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 10, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 10, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 10, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 5, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 10, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 10, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>0.5530</t>
+  </si>
+  <si>
+    <t>0.1301</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +201,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,88 +525,1446 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F101"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Best Parameters</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>CV Balanced Accuracy</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Test Balanced Accuracy</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 5, 'xgb__n_estimators': 300, 'xgb__subsample': 1.0}</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.8738095238095238</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.5606060606060606</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RF</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.6317460317460317</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.4090909090909091</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.6515151515151515</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>0.71904761904761905</v>
+      </c>
+      <c r="D2">
+        <v>0.72727272727272729</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>0.70714285714285718</v>
+      </c>
+      <c r="D3">
+        <v>0.56060606060606055</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D4">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>0.51269841269841276</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>0.58849206349206351</v>
+      </c>
+      <c r="D6">
+        <v>0.62121212121212122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>0.51865079365079358</v>
+      </c>
+      <c r="D7">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>0.61150793650793644</v>
+      </c>
+      <c r="D8">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>0.71071428571428574</v>
+      </c>
+      <c r="D9">
+        <v>0.78787878787878785</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>0.64642857142857146</v>
+      </c>
+      <c r="D10">
+        <v>0.43939393939393928</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>0.62976190476190474</v>
+      </c>
+      <c r="D11">
+        <v>0.56060606060606055</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>0.60039682539682537</v>
+      </c>
+      <c r="D12">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>0.55198412698412691</v>
+      </c>
+      <c r="D13">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>0.63849206349206356</v>
+      </c>
+      <c r="D14">
+        <v>0.53030303030303028</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>0.58174603174603179</v>
+      </c>
+      <c r="D15">
+        <v>0.74242424242424243</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>0.54761904761904756</v>
+      </c>
+      <c r="D16">
+        <v>0.81818181818181812</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D17">
+        <v>0.39393939393939392</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>0.66190476190476188</v>
+      </c>
+      <c r="D18">
+        <v>0.43939393939393928</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>0.53730158730158728</v>
+      </c>
+      <c r="D19">
+        <v>0.74242424242424243</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>0.55595238095238109</v>
+      </c>
+      <c r="D20">
+        <v>0.48484848484848492</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>0.51626984126984132</v>
+      </c>
+      <c r="D21">
+        <v>0.39393939393939392</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>0.67142857142857137</v>
+      </c>
+      <c r="D22">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>0.67420634920634914</v>
+      </c>
+      <c r="D23">
+        <v>0.36363636363636359</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>0.66150793650793649</v>
+      </c>
+      <c r="D24">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>0.58690476190476193</v>
+      </c>
+      <c r="D25">
+        <v>0.62121212121212122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="D26">
+        <v>0.48484848484848492</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>0.7071428571428573</v>
+      </c>
+      <c r="D27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>0.62261904761904763</v>
+      </c>
+      <c r="D28">
+        <v>0.65151515151515149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>0.51111111111111107</v>
+      </c>
+      <c r="D29">
+        <v>0.77272727272727271</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>0.58531746031746035</v>
+      </c>
+      <c r="D30">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31">
+        <v>0.5</v>
+      </c>
+      <c r="D31">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>0.6781746031746031</v>
+      </c>
+      <c r="D32">
+        <v>0.34848484848484851</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>0.5718253968253969</v>
+      </c>
+      <c r="D33">
+        <v>0.81818181818181812</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>0.63293650793650802</v>
+      </c>
+      <c r="D34">
+        <v>0.90909090909090917</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35">
+        <v>0.68373015873015863</v>
+      </c>
+      <c r="D35">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>0.54523809523809519</v>
+      </c>
+      <c r="D36">
+        <v>0.22727272727272729</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37">
+        <v>0.53650793650793649</v>
+      </c>
+      <c r="D37">
+        <v>0.74242424242424243</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38">
+        <v>0.67103174603174598</v>
+      </c>
+      <c r="D38">
+        <v>0.86363636363636365</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39">
+        <v>0.57063492063492072</v>
+      </c>
+      <c r="D39">
+        <v>0.86363636363636365</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40">
+        <v>0.64841269841269844</v>
+      </c>
+      <c r="D40">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41">
+        <v>0.60277777777777775</v>
+      </c>
+      <c r="D41">
+        <v>0.74242424242424243</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>0.67698412698412691</v>
+      </c>
+      <c r="D42">
+        <v>0.62121212121212122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43">
+        <v>0.64880952380952384</v>
+      </c>
+      <c r="D43">
+        <v>0.65151515151515149</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>0.58690476190476193</v>
+      </c>
+      <c r="D44">
+        <v>0.43939393939393928</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <v>0.71984126984126984</v>
+      </c>
+      <c r="D45">
+        <v>0.43939393939393928</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46">
+        <v>0.60238095238095235</v>
+      </c>
+      <c r="D46">
+        <v>0.60606060606060597</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47">
+        <v>0.56626984126984137</v>
+      </c>
+      <c r="D47">
+        <v>0.68181818181818188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48">
+        <v>0.63809523809523805</v>
+      </c>
+      <c r="D48">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49">
+        <v>0.69404761904761914</v>
+      </c>
+      <c r="D49">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50">
+        <v>0.66349206349206347</v>
+      </c>
+      <c r="D50">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51">
+        <v>0.67380952380952375</v>
+      </c>
+      <c r="D51">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E51" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52">
+        <v>0.74087301587301591</v>
+      </c>
+      <c r="D52">
+        <v>0.43939393939393928</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53">
+        <v>0.57539682539682546</v>
+      </c>
+      <c r="D53">
+        <v>0.56060606060606055</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54">
+        <v>0.57341269841269848</v>
+      </c>
+      <c r="D54">
+        <v>0.53030303030303028</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55">
+        <v>0.55952380952380953</v>
+      </c>
+      <c r="D55">
+        <v>0.83333333333333326</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56">
+        <v>0.58373015873015877</v>
+      </c>
+      <c r="D56">
+        <v>0.60606060606060597</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57">
+        <v>0.67420634920634914</v>
+      </c>
+      <c r="D57">
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58">
+        <v>0.63730158730158737</v>
+      </c>
+      <c r="D58">
+        <v>0.60606060606060597</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59">
+        <v>0.71984126984126995</v>
+      </c>
+      <c r="D59">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60">
+        <v>0.6166666666666667</v>
+      </c>
+      <c r="D60">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61">
+        <v>0.63373015873015881</v>
+      </c>
+      <c r="D61">
+        <v>0.77272727272727271</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62">
+        <v>0.6436507936507937</v>
+      </c>
+      <c r="D62">
+        <v>0.48484848484848492</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63">
+        <v>0.65555555555555556</v>
+      </c>
+      <c r="D63">
+        <v>0.53030303030303028</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64">
+        <v>0.6972222222222223</v>
+      </c>
+      <c r="D64">
+        <v>0.40909090909090912</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>14</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65">
+        <v>0.59087301587301588</v>
+      </c>
+      <c r="D65">
+        <v>0.65151515151515149</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66">
+        <v>0.66865079365079361</v>
+      </c>
+      <c r="D66">
+        <v>0.60606060606060597</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>14</v>
+      </c>
+      <c r="B67" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67">
+        <v>0.68174603174603166</v>
+      </c>
+      <c r="D67">
+        <v>0.40909090909090912</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D68">
+        <v>0.36363636363636359</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>14</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69">
+        <v>0.625</v>
+      </c>
+      <c r="D69">
+        <v>0.65151515151515149</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>14</v>
+      </c>
+      <c r="B70" t="s">
+        <v>28</v>
+      </c>
+      <c r="C70">
+        <v>0.57817460317460323</v>
+      </c>
+      <c r="D70">
+        <v>0.62121212121212122</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>14</v>
+      </c>
+      <c r="B71" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71">
+        <v>0.64682539682539686</v>
+      </c>
+      <c r="D71">
+        <v>0.53030303030303028</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" t="s">
+        <v>30</v>
+      </c>
+      <c r="C72">
+        <v>0.57936507936507931</v>
+      </c>
+      <c r="D72">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73">
+        <v>0.59365079365079365</v>
+      </c>
+      <c r="D73">
+        <v>0.43939393939393928</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74">
+        <v>0.65952380952380951</v>
+      </c>
+      <c r="D74">
+        <v>0.45454545454545447</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>14</v>
+      </c>
+      <c r="B75" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75">
+        <v>0.69841269841269848</v>
+      </c>
+      <c r="D75">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76" t="s">
+        <v>34</v>
+      </c>
+      <c r="C76">
+        <v>0.63809523809523805</v>
+      </c>
+      <c r="D76">
+        <v>0.48484848484848492</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>14</v>
+      </c>
+      <c r="B77" t="s">
+        <v>35</v>
+      </c>
+      <c r="C77">
+        <v>0.6436507936507937</v>
+      </c>
+      <c r="D77">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78">
+        <v>0.66309523809523807</v>
+      </c>
+      <c r="D78">
+        <v>0.74242424242424243</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" t="s">
+        <v>36</v>
+      </c>
+      <c r="C79">
+        <v>0.60476190476190483</v>
+      </c>
+      <c r="D79">
+        <v>0.60606060606060597</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>14</v>
+      </c>
+      <c r="B80" t="s">
+        <v>37</v>
+      </c>
+      <c r="C80">
+        <v>0.70952380952380956</v>
+      </c>
+      <c r="D80">
+        <v>0.74242424242424243</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" t="s">
+        <v>37</v>
+      </c>
+      <c r="C81">
+        <v>0.55119047619047623</v>
+      </c>
+      <c r="D81">
+        <v>0.40909090909090912</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" t="s">
+        <v>38</v>
+      </c>
+      <c r="C82">
+        <v>0.6075396825396826</v>
+      </c>
+      <c r="D82">
+        <v>0.39393939393939392</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" t="s">
+        <v>39</v>
+      </c>
+      <c r="C83">
+        <v>0.57420634920634928</v>
+      </c>
+      <c r="D83">
+        <v>0.74242424242424243</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" t="s">
+        <v>25</v>
+      </c>
+      <c r="C84">
+        <v>0.64404761904761909</v>
+      </c>
+      <c r="D84">
+        <v>0.53030303030303028</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85">
+        <v>0.68452380952380965</v>
+      </c>
+      <c r="D85">
+        <v>0.62121212121212122</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C86">
+        <v>0.58849206349206351</v>
+      </c>
+      <c r="D86">
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>14</v>
+      </c>
+      <c r="B87" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D87">
+        <v>0.74242424242424243</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88">
+        <v>0.66269841269841268</v>
+      </c>
+      <c r="D88">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>14</v>
+      </c>
+      <c r="B89" t="s">
+        <v>41</v>
+      </c>
+      <c r="C89">
+        <v>0.69087301587301597</v>
+      </c>
+      <c r="D89">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>14</v>
+      </c>
+      <c r="B90" t="s">
+        <v>42</v>
+      </c>
+      <c r="C90">
+        <v>0.72103174603174602</v>
+      </c>
+      <c r="D90">
+        <v>0.62121212121212122</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91">
+        <v>0.63253968253968251</v>
+      </c>
+      <c r="D91">
+        <v>0.56060606060606055</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" t="s">
+        <v>43</v>
+      </c>
+      <c r="C92">
+        <v>0.60555555555555551</v>
+      </c>
+      <c r="D92">
+        <v>0.62121212121212122</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>14</v>
+      </c>
+      <c r="B93" t="s">
+        <v>35</v>
+      </c>
+      <c r="C93">
+        <v>0.70515873015873021</v>
+      </c>
+      <c r="D93">
+        <v>0.31818181818181818</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B94" t="s">
+        <v>44</v>
+      </c>
+      <c r="C94">
+        <v>0.60396825396825393</v>
+      </c>
+      <c r="D94">
+        <v>0.31818181818181818</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>14</v>
+      </c>
+      <c r="B95" t="s">
+        <v>25</v>
+      </c>
+      <c r="C95">
+        <v>0.69444444444444431</v>
+      </c>
+      <c r="D95">
+        <v>0.43939393939393928</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>14</v>
+      </c>
+      <c r="B96" t="s">
+        <v>32</v>
+      </c>
+      <c r="C96">
+        <v>0.63650793650793647</v>
+      </c>
+      <c r="D96">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>14</v>
+      </c>
+      <c r="B97" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97">
+        <v>0.54484126984126979</v>
+      </c>
+      <c r="D97">
+        <v>0.65151515151515149</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>14</v>
+      </c>
+      <c r="B98" t="s">
+        <v>41</v>
+      </c>
+      <c r="C98">
+        <v>0.66111111111111109</v>
+      </c>
+      <c r="D98">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>14</v>
+      </c>
+      <c r="B99" t="s">
+        <v>42</v>
+      </c>
+      <c r="C99">
+        <v>0.69087301587301597</v>
+      </c>
+      <c r="D99">
+        <v>0.53030303030303028</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>14</v>
+      </c>
+      <c r="B100" t="s">
+        <v>45</v>
+      </c>
+      <c r="C100">
+        <v>0.57420634920634928</v>
+      </c>
+      <c r="D100">
+        <v>0.56060606060606055</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>14</v>
+      </c>
+      <c r="B101" t="s">
+        <v>21</v>
+      </c>
+      <c r="C101">
+        <v>0.65873015873015872</v>
+      </c>
+      <c r="D101">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E101" t="s">
+        <v>46</v>
+      </c>
+      <c r="F101" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/results_coherence.xlsx
+++ b/results_coherence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_74212A8AD049320F62355476585DCE3A874707F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D3344F0-687C-4C96-B917-91E0BCD7F7C8}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_573D3848504BB40E62355476585DCE3A874663F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A0E43B0-77A5-4493-8261-D5B996CA0258}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="82">
   <si>
     <t>Model</t>
   </si>
@@ -164,6 +164,108 @@
   </si>
   <si>
     <t>0.1301</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 5, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>0.5312</t>
+  </si>
+  <si>
+    <t>0.1309</t>
   </si>
 </sst>
 </file>
@@ -526,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1967,6 +2069,712 @@
         <v>47</v>
       </c>
     </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>48</v>
+      </c>
+      <c r="B102" t="s">
+        <v>49</v>
+      </c>
+      <c r="C102">
+        <v>0.72579365079365077</v>
+      </c>
+      <c r="D102">
+        <v>0.48484848484848492</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>48</v>
+      </c>
+      <c r="B103" t="s">
+        <v>50</v>
+      </c>
+      <c r="C103">
+        <v>0.65357142857142858</v>
+      </c>
+      <c r="D103">
+        <v>0.51515151515151514</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>48</v>
+      </c>
+      <c r="B104" t="s">
+        <v>51</v>
+      </c>
+      <c r="C104">
+        <v>0.60277777777777775</v>
+      </c>
+      <c r="D104">
+        <v>0.56060606060606055</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>48</v>
+      </c>
+      <c r="B105" t="s">
+        <v>52</v>
+      </c>
+      <c r="C105">
+        <v>0.59603174603174602</v>
+      </c>
+      <c r="D105">
+        <v>0.60606060606060597</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>48</v>
+      </c>
+      <c r="B106" t="s">
+        <v>53</v>
+      </c>
+      <c r="C106">
+        <v>0.64682539682539675</v>
+      </c>
+      <c r="D106">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>48</v>
+      </c>
+      <c r="B107" t="s">
+        <v>54</v>
+      </c>
+      <c r="C107">
+        <v>0.69761904761904769</v>
+      </c>
+      <c r="D107">
+        <v>0.53030303030303028</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>48</v>
+      </c>
+      <c r="B108" t="s">
+        <v>55</v>
+      </c>
+      <c r="C108">
+        <v>0.60793650793650789</v>
+      </c>
+      <c r="D108">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>48</v>
+      </c>
+      <c r="B109" t="s">
+        <v>56</v>
+      </c>
+      <c r="C109">
+        <v>0.6968253968253969</v>
+      </c>
+      <c r="D109">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>48</v>
+      </c>
+      <c r="B110" t="s">
+        <v>56</v>
+      </c>
+      <c r="C110">
+        <v>0.6515873015873016</v>
+      </c>
+      <c r="D110">
+        <v>0.53030303030303028</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>48</v>
+      </c>
+      <c r="B111" t="s">
+        <v>57</v>
+      </c>
+      <c r="C111">
+        <v>0.70119047619047625</v>
+      </c>
+      <c r="D111">
+        <v>0.59090909090909094</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>48</v>
+      </c>
+      <c r="B112" t="s">
+        <v>54</v>
+      </c>
+      <c r="C112">
+        <v>0.60476190476190483</v>
+      </c>
+      <c r="D112">
+        <v>0.43939393939393928</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>48</v>
+      </c>
+      <c r="B113" t="s">
+        <v>58</v>
+      </c>
+      <c r="C113">
+        <v>0.64047619047619053</v>
+      </c>
+      <c r="D113">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>48</v>
+      </c>
+      <c r="B114" t="s">
+        <v>59</v>
+      </c>
+      <c r="C114">
+        <v>0.58611111111111114</v>
+      </c>
+      <c r="D114">
+        <v>0.48484848484848492</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>48</v>
+      </c>
+      <c r="B115" t="s">
+        <v>51</v>
+      </c>
+      <c r="C115">
+        <v>0.74365079365079367</v>
+      </c>
+      <c r="D115">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>48</v>
+      </c>
+      <c r="B116" t="s">
+        <v>60</v>
+      </c>
+      <c r="C116">
+        <v>0.67738095238095231</v>
+      </c>
+      <c r="D116">
+        <v>0.43939393939393928</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>48</v>
+      </c>
+      <c r="B117" t="s">
+        <v>61</v>
+      </c>
+      <c r="C117">
+        <v>0.59246031746031746</v>
+      </c>
+      <c r="D117">
+        <v>0.31818181818181818</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>48</v>
+      </c>
+      <c r="B118" t="s">
+        <v>56</v>
+      </c>
+      <c r="C118">
+        <v>0.65952380952380951</v>
+      </c>
+      <c r="D118">
+        <v>0.31818181818181818</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>48</v>
+      </c>
+      <c r="B119" t="s">
+        <v>62</v>
+      </c>
+      <c r="C119">
+        <v>0.67896825396825411</v>
+      </c>
+      <c r="D119">
+        <v>0.65151515151515149</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>48</v>
+      </c>
+      <c r="B120" t="s">
+        <v>63</v>
+      </c>
+      <c r="C120">
+        <v>0.55634920634920637</v>
+      </c>
+      <c r="D120">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>48</v>
+      </c>
+      <c r="B121" t="s">
+        <v>64</v>
+      </c>
+      <c r="C121">
+        <v>0.68492063492063482</v>
+      </c>
+      <c r="D121">
+        <v>0.43939393939393928</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>48</v>
+      </c>
+      <c r="B122" t="s">
+        <v>65</v>
+      </c>
+      <c r="C122">
+        <v>0.53174603174603174</v>
+      </c>
+      <c r="D122">
+        <v>0.62121212121212122</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>48</v>
+      </c>
+      <c r="B123" t="s">
+        <v>66</v>
+      </c>
+      <c r="C123">
+        <v>0.57658730158730165</v>
+      </c>
+      <c r="D123">
+        <v>0.60606060606060597</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>48</v>
+      </c>
+      <c r="B124" t="s">
+        <v>67</v>
+      </c>
+      <c r="C124">
+        <v>0.76071428571428579</v>
+      </c>
+      <c r="D124">
+        <v>0.22727272727272729</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>48</v>
+      </c>
+      <c r="B125" t="s">
+        <v>56</v>
+      </c>
+      <c r="C125">
+        <v>0.77579365079365081</v>
+      </c>
+      <c r="D125">
+        <v>0.45454545454545447</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>48</v>
+      </c>
+      <c r="B126" t="s">
+        <v>68</v>
+      </c>
+      <c r="C126">
+        <v>0.62341269841269842</v>
+      </c>
+      <c r="D126">
+        <v>0.60606060606060597</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>48</v>
+      </c>
+      <c r="B127" t="s">
+        <v>69</v>
+      </c>
+      <c r="C127">
+        <v>0.71349206349206351</v>
+      </c>
+      <c r="D127">
+        <v>0.45454545454545447</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>48</v>
+      </c>
+      <c r="B128" t="s">
+        <v>70</v>
+      </c>
+      <c r="C128">
+        <v>0.71031746031746035</v>
+      </c>
+      <c r="D128">
+        <v>0.78787878787878785</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>48</v>
+      </c>
+      <c r="B129" t="s">
+        <v>51</v>
+      </c>
+      <c r="C129">
+        <v>0.65595238095238095</v>
+      </c>
+      <c r="D129">
+        <v>0.65151515151515149</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>48</v>
+      </c>
+      <c r="B130" t="s">
+        <v>71</v>
+      </c>
+      <c r="C130">
+        <v>0.74285714285714288</v>
+      </c>
+      <c r="D130">
+        <v>0.5757575757575758</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>48</v>
+      </c>
+      <c r="B131" t="s">
+        <v>72</v>
+      </c>
+      <c r="C131">
+        <v>0.5</v>
+      </c>
+      <c r="D131">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>48</v>
+      </c>
+      <c r="B132" t="s">
+        <v>51</v>
+      </c>
+      <c r="C132">
+        <v>0.63293650793650791</v>
+      </c>
+      <c r="D132">
+        <v>0.2121212121212121</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>48</v>
+      </c>
+      <c r="B133" t="s">
+        <v>73</v>
+      </c>
+      <c r="C133">
+        <v>0.69761904761904747</v>
+      </c>
+      <c r="D133">
+        <v>0.48484848484848492</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>48</v>
+      </c>
+      <c r="B134" t="s">
+        <v>50</v>
+      </c>
+      <c r="C134">
+        <v>0.69603174603174611</v>
+      </c>
+      <c r="D134">
+        <v>0.53030303030303028</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>48</v>
+      </c>
+      <c r="B135" t="s">
+        <v>74</v>
+      </c>
+      <c r="C135">
+        <v>0.78769841269841268</v>
+      </c>
+      <c r="D135">
+        <v>0.53030303030303028</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>48</v>
+      </c>
+      <c r="B136" t="s">
+        <v>75</v>
+      </c>
+      <c r="C136">
+        <v>0.67619047619047612</v>
+      </c>
+      <c r="D136">
+        <v>0.43939393939393928</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>48</v>
+      </c>
+      <c r="B137" t="s">
+        <v>73</v>
+      </c>
+      <c r="C137">
+        <v>0.625</v>
+      </c>
+      <c r="D137">
+        <v>0.74242424242424243</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>48</v>
+      </c>
+      <c r="B138" t="s">
+        <v>58</v>
+      </c>
+      <c r="C138">
+        <v>0.74642857142857144</v>
+      </c>
+      <c r="D138">
+        <v>0.78787878787878785</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>48</v>
+      </c>
+      <c r="B139" t="s">
+        <v>76</v>
+      </c>
+      <c r="C139">
+        <v>0.72817460317460325</v>
+      </c>
+      <c r="D139">
+        <v>0.39393939393939392</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>48</v>
+      </c>
+      <c r="B140" t="s">
+        <v>50</v>
+      </c>
+      <c r="C140">
+        <v>0.70039682539682546</v>
+      </c>
+      <c r="D140">
+        <v>0.60606060606060597</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>48</v>
+      </c>
+      <c r="B141" t="s">
+        <v>77</v>
+      </c>
+      <c r="C141">
+        <v>0.62182539682539684</v>
+      </c>
+      <c r="D141">
+        <v>0.43939393939393928</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>48</v>
+      </c>
+      <c r="B142" t="s">
+        <v>62</v>
+      </c>
+      <c r="C142">
+        <v>0.6968253968253969</v>
+      </c>
+      <c r="D142">
+        <v>0.62121212121212122</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>48</v>
+      </c>
+      <c r="B143" t="s">
+        <v>50</v>
+      </c>
+      <c r="C143">
+        <v>0.86190476190476184</v>
+      </c>
+      <c r="D143">
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>48</v>
+      </c>
+      <c r="B144" t="s">
+        <v>57</v>
+      </c>
+      <c r="C144">
+        <v>0.66785714285714282</v>
+      </c>
+      <c r="D144">
+        <v>0.56060606060606055</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>48</v>
+      </c>
+      <c r="B145" t="s">
+        <v>78</v>
+      </c>
+      <c r="C145">
+        <v>0.71547619047619049</v>
+      </c>
+      <c r="D145">
+        <v>0.48484848484848492</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>48</v>
+      </c>
+      <c r="B146" t="s">
+        <v>77</v>
+      </c>
+      <c r="C146">
+        <v>0.72658730158730156</v>
+      </c>
+      <c r="D146">
+        <v>0.53030303030303028</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>48</v>
+      </c>
+      <c r="B147" t="s">
+        <v>51</v>
+      </c>
+      <c r="C147">
+        <v>0.55436507936507951</v>
+      </c>
+      <c r="D147">
+        <v>0.65151515151515149</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>48</v>
+      </c>
+      <c r="B148" t="s">
+        <v>79</v>
+      </c>
+      <c r="C148">
+        <v>0.794047619047619</v>
+      </c>
+      <c r="D148">
+        <v>0.45454545454545447</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>48</v>
+      </c>
+      <c r="B149" t="s">
+        <v>61</v>
+      </c>
+      <c r="C149">
+        <v>0.68690476190476202</v>
+      </c>
+      <c r="D149">
+        <v>0.53030303030303028</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>48</v>
+      </c>
+      <c r="B150" t="s">
+        <v>63</v>
+      </c>
+      <c r="C150">
+        <v>0.65079365079365081</v>
+      </c>
+      <c r="D150">
+        <v>0.56060606060606055</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>48</v>
+      </c>
+      <c r="B151" t="s">
+        <v>54</v>
+      </c>
+      <c r="C151">
+        <v>0.66865079365079361</v>
+      </c>
+      <c r="D151">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="E151" t="s">
+        <v>80</v>
+      </c>
+      <c r="F151" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results_coherence.xlsx
+++ b/results_coherence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_573D3848504BB40E62355476585DCE3A874663F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A0E43B0-77A5-4493-8261-D5B996CA0258}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_573D3848504BB40E62355476585DCE3A874663F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EBC069C-340D-4908-9591-B83E74F0F354}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="72">
   <si>
     <t>Model</t>
   </si>
@@ -34,12 +34,6 @@
     <t>Test Balanced Accuracy</t>
   </si>
   <si>
-    <t>Unnamed: 4</t>
-  </si>
-  <si>
-    <t>Unnamed: 5</t>
-  </si>
-  <si>
     <t>SVM</t>
   </si>
   <si>
@@ -52,18 +46,6 @@
     <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'rbf'}</t>
   </si>
   <si>
-    <t>MEAN</t>
-  </si>
-  <si>
-    <t>STD</t>
-  </si>
-  <si>
-    <t>0.6288</t>
-  </si>
-  <si>
-    <t>0.1590</t>
-  </si>
-  <si>
     <t>RF</t>
   </si>
   <si>
@@ -160,12 +142,6 @@
     <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
   </si>
   <si>
-    <t>0.5530</t>
-  </si>
-  <si>
-    <t>0.1301</t>
-  </si>
-  <si>
     <t>XGBoost</t>
   </si>
   <si>
@@ -260,12 +236,6 @@
   </si>
   <si>
     <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
-  </si>
-  <si>
-    <t>0.5312</t>
-  </si>
-  <si>
-    <t>0.1309</t>
   </si>
 </sst>
 </file>
@@ -294,7 +264,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -317,13 +287,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -641,22 +630,18 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>0.71904761904761905</v>
@@ -667,10 +652,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>0.70714285714285718</v>
@@ -681,10 +666,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
       </c>
       <c r="C4">
         <v>0.54166666666666663</v>
@@ -695,10 +680,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>0.51269841269841276</v>
@@ -709,10 +694,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>0.58849206349206351</v>
@@ -723,10 +708,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>0.51865079365079358</v>
@@ -737,10 +722,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>0.61150793650793644</v>
@@ -751,10 +736,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>0.71071428571428574</v>
@@ -765,10 +750,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>0.64642857142857146</v>
@@ -779,10 +764,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>0.62976190476190474</v>
@@ -793,10 +778,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>0.60039682539682537</v>
@@ -807,10 +792,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>0.55198412698412691</v>
@@ -821,10 +806,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14">
         <v>0.63849206349206356</v>
@@ -835,10 +820,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>0.58174603174603179</v>
@@ -849,10 +834,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>0.54761904761904756</v>
@@ -863,10 +848,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
         <v>6</v>
-      </c>
-      <c r="B17" t="s">
-        <v>8</v>
       </c>
       <c r="C17">
         <v>0.61111111111111105</v>
@@ -877,10 +862,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>0.66190476190476188</v>
@@ -891,10 +876,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>0.53730158730158728</v>
@@ -905,10 +890,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>0.55595238095238109</v>
@@ -919,10 +904,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>0.51626984126984132</v>
@@ -933,10 +918,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>0.67142857142857137</v>
@@ -947,10 +932,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C23">
         <v>0.67420634920634914</v>
@@ -961,10 +946,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>0.66150793650793649</v>
@@ -975,10 +960,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>0.58690476190476193</v>
@@ -989,10 +974,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>0.52380952380952384</v>
@@ -1003,10 +988,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>0.7071428571428573</v>
@@ -1017,10 +1002,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28">
         <v>0.62261904761904763</v>
@@ -1031,10 +1016,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
         <v>6</v>
-      </c>
-      <c r="B29" t="s">
-        <v>8</v>
       </c>
       <c r="C29">
         <v>0.51111111111111107</v>
@@ -1045,10 +1030,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>0.58531746031746035</v>
@@ -1059,10 +1044,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C31">
         <v>0.5</v>
@@ -1073,10 +1058,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C32">
         <v>0.6781746031746031</v>
@@ -1087,10 +1072,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C33">
         <v>0.5718253968253969</v>
@@ -1101,10 +1086,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C34">
         <v>0.63293650793650802</v>
@@ -1115,10 +1100,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>0.68373015873015863</v>
@@ -1129,10 +1114,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>0.54523809523809519</v>
@@ -1143,10 +1128,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>0.53650793650793649</v>
@@ -1157,10 +1142,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>0.67103174603174598</v>
@@ -1171,10 +1156,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>0.57063492063492072</v>
@@ -1185,10 +1170,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>0.64841269841269844</v>
@@ -1199,10 +1184,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C41">
         <v>0.60277777777777775</v>
@@ -1213,10 +1198,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C42">
         <v>0.67698412698412691</v>
@@ -1227,10 +1212,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>0.64880952380952384</v>
@@ -1241,10 +1226,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C44">
         <v>0.58690476190476193</v>
@@ -1255,10 +1240,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C45">
         <v>0.71984126984126984</v>
@@ -1269,10 +1254,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C46">
         <v>0.60238095238095235</v>
@@ -1283,10 +1268,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C47">
         <v>0.56626984126984137</v>
@@ -1297,10 +1282,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C48">
         <v>0.63809523809523805</v>
@@ -1309,12 +1294,12 @@
         <v>0.69696969696969702</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C49">
         <v>0.69404761904761914</v>
@@ -1323,12 +1308,12 @@
         <v>0.5757575757575758</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C50">
         <v>0.66349206349206347</v>
@@ -1336,19 +1321,13 @@
       <c r="D50">
         <v>0.72727272727272729</v>
       </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C51">
         <v>0.67380952380952375</v>
@@ -1356,19 +1335,13 @@
       <c r="D51">
         <v>0.74242424242424243</v>
       </c>
-      <c r="E51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C52">
         <v>0.74087301587301591</v>
@@ -1377,12 +1350,12 @@
         <v>0.43939393939393928</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C53">
         <v>0.57539682539682546</v>
@@ -1391,12 +1364,12 @@
         <v>0.56060606060606055</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C54">
         <v>0.57341269841269848</v>
@@ -1405,12 +1378,12 @@
         <v>0.53030303030303028</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C55">
         <v>0.55952380952380953</v>
@@ -1419,12 +1392,12 @@
         <v>0.83333333333333326</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C56">
         <v>0.58373015873015877</v>
@@ -1433,12 +1406,12 @@
         <v>0.60606060606060597</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" t="s">
         <v>14</v>
-      </c>
-      <c r="B57" t="s">
-        <v>20</v>
       </c>
       <c r="C57">
         <v>0.67420634920634914</v>
@@ -1447,12 +1420,12 @@
         <v>0.27272727272727271</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C58">
         <v>0.63730158730158737</v>
@@ -1461,12 +1434,12 @@
         <v>0.60606060606060597</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C59">
         <v>0.71984126984126995</v>
@@ -1475,12 +1448,12 @@
         <v>0.69696969696969702</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C60">
         <v>0.6166666666666667</v>
@@ -1489,12 +1462,12 @@
         <v>0.5757575757575758</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C61">
         <v>0.63373015873015881</v>
@@ -1503,12 +1476,12 @@
         <v>0.77272727272727271</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C62">
         <v>0.6436507936507937</v>
@@ -1517,12 +1490,12 @@
         <v>0.48484848484848492</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C63">
         <v>0.65555555555555556</v>
@@ -1531,12 +1504,12 @@
         <v>0.53030303030303028</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C64">
         <v>0.6972222222222223</v>
@@ -1547,10 +1520,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C65">
         <v>0.59087301587301588</v>
@@ -1561,10 +1534,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C66">
         <v>0.66865079365079361</v>
@@ -1575,10 +1548,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" t="s">
         <v>14</v>
-      </c>
-      <c r="B67" t="s">
-        <v>20</v>
       </c>
       <c r="C67">
         <v>0.68174603174603166</v>
@@ -1589,10 +1562,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C68">
         <v>0.63888888888888884</v>
@@ -1603,10 +1576,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C69">
         <v>0.625</v>
@@ -1617,10 +1590,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C70">
         <v>0.57817460317460323</v>
@@ -1631,10 +1604,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C71">
         <v>0.64682539682539686</v>
@@ -1645,10 +1618,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C72">
         <v>0.57936507936507931</v>
@@ -1659,10 +1632,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C73">
         <v>0.59365079365079365</v>
@@ -1673,10 +1646,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C74">
         <v>0.65952380952380951</v>
@@ -1687,10 +1660,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C75">
         <v>0.69841269841269848</v>
@@ -1701,10 +1674,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C76">
         <v>0.63809523809523805</v>
@@ -1715,10 +1688,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C77">
         <v>0.6436507936507937</v>
@@ -1729,10 +1702,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" t="s">
         <v>14</v>
-      </c>
-      <c r="B78" t="s">
-        <v>20</v>
       </c>
       <c r="C78">
         <v>0.66309523809523807</v>
@@ -1743,10 +1716,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C79">
         <v>0.60476190476190483</v>
@@ -1757,10 +1730,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C80">
         <v>0.70952380952380956</v>
@@ -1771,10 +1744,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C81">
         <v>0.55119047619047623</v>
@@ -1785,10 +1758,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C82">
         <v>0.6075396825396826</v>
@@ -1799,10 +1772,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C83">
         <v>0.57420634920634928</v>
@@ -1813,10 +1786,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C84">
         <v>0.64404761904761909</v>
@@ -1827,10 +1800,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85" t="s">
         <v>14</v>
-      </c>
-      <c r="B85" t="s">
-        <v>20</v>
       </c>
       <c r="C85">
         <v>0.68452380952380965</v>
@@ -1841,10 +1814,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C86">
         <v>0.58849206349206351</v>
@@ -1855,10 +1828,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C87">
         <v>0.63888888888888884</v>
@@ -1869,10 +1842,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" t="s">
         <v>14</v>
-      </c>
-      <c r="B88" t="s">
-        <v>20</v>
       </c>
       <c r="C88">
         <v>0.66269841269841268</v>
@@ -1883,10 +1856,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C89">
         <v>0.69087301587301597</v>
@@ -1897,10 +1870,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C90">
         <v>0.72103174603174602</v>
@@ -1911,10 +1884,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C91">
         <v>0.63253968253968251</v>
@@ -1925,10 +1898,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C92">
         <v>0.60555555555555551</v>
@@ -1939,10 +1912,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C93">
         <v>0.70515873015873021</v>
@@ -1953,10 +1926,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C94">
         <v>0.60396825396825393</v>
@@ -1967,10 +1940,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C95">
         <v>0.69444444444444431</v>
@@ -1981,10 +1954,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C96">
         <v>0.63650793650793647</v>
@@ -1993,12 +1966,12 @@
         <v>0.5757575757575758</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C97">
         <v>0.54484126984126979</v>
@@ -2007,12 +1980,12 @@
         <v>0.65151515151515149</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C98">
         <v>0.66111111111111109</v>
@@ -2021,12 +1994,12 @@
         <v>0.5757575757575758</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C99">
         <v>0.69087301587301597</v>
@@ -2035,12 +2008,12 @@
         <v>0.53030303030303028</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C100">
         <v>0.57420634920634928</v>
@@ -2049,12 +2022,12 @@
         <v>0.56060606060606055</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C101">
         <v>0.65873015873015872</v>
@@ -2062,19 +2035,13 @@
       <c r="D101">
         <v>0.65151515151515149</v>
       </c>
-      <c r="E101" t="s">
-        <v>46</v>
-      </c>
-      <c r="F101" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B102" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C102">
         <v>0.72579365079365077</v>
@@ -2083,12 +2050,12 @@
         <v>0.48484848484848492</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B103" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C103">
         <v>0.65357142857142858</v>
@@ -2097,12 +2064,12 @@
         <v>0.51515151515151514</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B104" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C104">
         <v>0.60277777777777775</v>
@@ -2111,12 +2078,12 @@
         <v>0.56060606060606055</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B105" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C105">
         <v>0.59603174603174602</v>
@@ -2125,12 +2092,12 @@
         <v>0.60606060606060597</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B106" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C106">
         <v>0.64682539682539675</v>
@@ -2139,12 +2106,12 @@
         <v>0.5757575757575758</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B107" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C107">
         <v>0.69761904761904769</v>
@@ -2153,12 +2120,12 @@
         <v>0.53030303030303028</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B108" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C108">
         <v>0.60793650793650789</v>
@@ -2167,12 +2134,12 @@
         <v>0.69696969696969702</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
+        <v>40</v>
+      </c>
+      <c r="B109" t="s">
         <v>48</v>
-      </c>
-      <c r="B109" t="s">
-        <v>56</v>
       </c>
       <c r="C109">
         <v>0.6968253968253969</v>
@@ -2181,12 +2148,12 @@
         <v>0.69696969696969702</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
+        <v>40</v>
+      </c>
+      <c r="B110" t="s">
         <v>48</v>
-      </c>
-      <c r="B110" t="s">
-        <v>56</v>
       </c>
       <c r="C110">
         <v>0.6515873015873016</v>
@@ -2195,12 +2162,12 @@
         <v>0.53030303030303028</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B111" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C111">
         <v>0.70119047619047625</v>
@@ -2209,12 +2176,12 @@
         <v>0.59090909090909094</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B112" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C112">
         <v>0.60476190476190483</v>
@@ -2225,10 +2192,10 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B113" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C113">
         <v>0.64047619047619053</v>
@@ -2239,10 +2206,10 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B114" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C114">
         <v>0.58611111111111114</v>
@@ -2253,10 +2220,10 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B115" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C115">
         <v>0.74365079365079367</v>
@@ -2267,10 +2234,10 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B116" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C116">
         <v>0.67738095238095231</v>
@@ -2281,10 +2248,10 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B117" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C117">
         <v>0.59246031746031746</v>
@@ -2295,10 +2262,10 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
+        <v>40</v>
+      </c>
+      <c r="B118" t="s">
         <v>48</v>
-      </c>
-      <c r="B118" t="s">
-        <v>56</v>
       </c>
       <c r="C118">
         <v>0.65952380952380951</v>
@@ -2309,10 +2276,10 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B119" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C119">
         <v>0.67896825396825411</v>
@@ -2323,10 +2290,10 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B120" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C120">
         <v>0.55634920634920637</v>
@@ -2337,10 +2304,10 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B121" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C121">
         <v>0.68492063492063482</v>
@@ -2351,10 +2318,10 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B122" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C122">
         <v>0.53174603174603174</v>
@@ -2365,10 +2332,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B123" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C123">
         <v>0.57658730158730165</v>
@@ -2379,10 +2346,10 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B124" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C124">
         <v>0.76071428571428579</v>
@@ -2393,10 +2360,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
+        <v>40</v>
+      </c>
+      <c r="B125" t="s">
         <v>48</v>
-      </c>
-      <c r="B125" t="s">
-        <v>56</v>
       </c>
       <c r="C125">
         <v>0.77579365079365081</v>
@@ -2407,10 +2374,10 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B126" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C126">
         <v>0.62341269841269842</v>
@@ -2421,10 +2388,10 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B127" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C127">
         <v>0.71349206349206351</v>
@@ -2435,10 +2402,10 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B128" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C128">
         <v>0.71031746031746035</v>
@@ -2449,10 +2416,10 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B129" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C129">
         <v>0.65595238095238095</v>
@@ -2463,10 +2430,10 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B130" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C130">
         <v>0.74285714285714288</v>
@@ -2477,10 +2444,10 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B131" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C131">
         <v>0.5</v>
@@ -2491,10 +2458,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B132" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C132">
         <v>0.63293650793650791</v>
@@ -2505,10 +2472,10 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B133" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C133">
         <v>0.69761904761904747</v>
@@ -2519,10 +2486,10 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B134" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C134">
         <v>0.69603174603174611</v>
@@ -2533,10 +2500,10 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B135" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C135">
         <v>0.78769841269841268</v>
@@ -2547,10 +2514,10 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B136" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C136">
         <v>0.67619047619047612</v>
@@ -2561,10 +2528,10 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B137" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C137">
         <v>0.625</v>
@@ -2575,10 +2542,10 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B138" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C138">
         <v>0.74642857142857144</v>
@@ -2589,10 +2556,10 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B139" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C139">
         <v>0.72817460317460325</v>
@@ -2603,10 +2570,10 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B140" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C140">
         <v>0.70039682539682546</v>
@@ -2617,10 +2584,10 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B141" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C141">
         <v>0.62182539682539684</v>
@@ -2631,10 +2598,10 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B142" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C142">
         <v>0.6968253968253969</v>
@@ -2645,10 +2612,10 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B143" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C143">
         <v>0.86190476190476184</v>
@@ -2659,10 +2626,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B144" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C144">
         <v>0.66785714285714282</v>
@@ -2671,12 +2638,12 @@
         <v>0.56060606060606055</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B145" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C145">
         <v>0.71547619047619049</v>
@@ -2685,12 +2652,12 @@
         <v>0.48484848484848492</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B146" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C146">
         <v>0.72658730158730156</v>
@@ -2699,12 +2666,12 @@
         <v>0.53030303030303028</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B147" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C147">
         <v>0.55436507936507951</v>
@@ -2713,12 +2680,12 @@
         <v>0.65151515151515149</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B148" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C148">
         <v>0.794047619047619</v>
@@ -2727,12 +2694,12 @@
         <v>0.45454545454545447</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B149" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C149">
         <v>0.68690476190476202</v>
@@ -2741,12 +2708,12 @@
         <v>0.53030303030303028</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B150" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C150">
         <v>0.65079365079365081</v>
@@ -2755,24 +2722,18 @@
         <v>0.56060606060606055</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B151" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C151">
         <v>0.66865079365079361</v>
       </c>
       <c r="D151">
         <v>0.39393939393939392</v>
-      </c>
-      <c r="E151" t="s">
-        <v>80</v>
-      </c>
-      <c r="F151" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/results_coherence.xlsx
+++ b/results_coherence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_573D3848504BB40E62355476585DCE3A874663F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EBC069C-340D-4908-9591-B83E74F0F354}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_74C1F017D6746E0E62355476585DCE3A8746D4A3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37A66B69-0925-4260-9CB7-12CFD974A5AA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="97">
   <si>
     <t>Model</t>
   </si>
@@ -236,6 +236,81 @@
   </si>
   <si>
     <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'svm__C': 1, 'svm__gamma': 'scale', 'svm__kernel': 'rbf'}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 10, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 10, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 5, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 10, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 10, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>beta</t>
   </si>
 </sst>
 </file>
@@ -291,28 +366,23 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="thin">
         <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -617,10 +687,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:E301"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,13 +700,14 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E1" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -649,8 +720,11 @@
       <c r="D2">
         <v>0.72727272727272729</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -663,8 +737,11 @@
       <c r="D3">
         <v>0.56060606060606055</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -677,8 +754,11 @@
       <c r="D4">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -691,8 +771,11 @@
       <c r="D5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -705,8 +788,11 @@
       <c r="D6">
         <v>0.62121212121212122</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -719,8 +805,11 @@
       <c r="D7">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -733,8 +822,11 @@
       <c r="D8">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -747,8 +839,11 @@
       <c r="D9">
         <v>0.78787878787878785</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -761,8 +856,11 @@
       <c r="D10">
         <v>0.43939393939393928</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -775,8 +873,11 @@
       <c r="D11">
         <v>0.56060606060606055</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -789,8 +890,11 @@
       <c r="D12">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -803,8 +907,11 @@
       <c r="D13">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -817,8 +924,11 @@
       <c r="D14">
         <v>0.53030303030303028</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -831,8 +941,11 @@
       <c r="D15">
         <v>0.74242424242424243</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -845,8 +958,11 @@
       <c r="D16">
         <v>0.81818181818181812</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -859,8 +975,11 @@
       <c r="D17">
         <v>0.39393939393939392</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -873,8 +992,11 @@
       <c r="D18">
         <v>0.43939393939393928</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -887,8 +1009,11 @@
       <c r="D19">
         <v>0.74242424242424243</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -901,8 +1026,11 @@
       <c r="D20">
         <v>0.48484848484848492</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -915,8 +1043,11 @@
       <c r="D21">
         <v>0.39393939393939392</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -929,8 +1060,11 @@
       <c r="D22">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -943,8 +1077,11 @@
       <c r="D23">
         <v>0.36363636363636359</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -957,8 +1094,11 @@
       <c r="D24">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E24" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -971,8 +1111,11 @@
       <c r="D25">
         <v>0.62121212121212122</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -985,8 +1128,11 @@
       <c r="D26">
         <v>0.48484848484848492</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E26" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -999,8 +1145,11 @@
       <c r="D27">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1013,8 +1162,11 @@
       <c r="D28">
         <v>0.65151515151515149</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1027,8 +1179,11 @@
       <c r="D29">
         <v>0.77272727272727271</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1041,8 +1196,11 @@
       <c r="D30">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E30" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -1055,8 +1213,11 @@
       <c r="D31">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -1069,8 +1230,11 @@
       <c r="D32">
         <v>0.34848484848484851</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -1083,8 +1247,11 @@
       <c r="D33">
         <v>0.81818181818181812</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -1097,8 +1264,11 @@
       <c r="D34">
         <v>0.90909090909090917</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E34" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -1111,8 +1281,11 @@
       <c r="D35">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1125,8 +1298,11 @@
       <c r="D36">
         <v>0.22727272727272729</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -1139,8 +1315,11 @@
       <c r="D37">
         <v>0.74242424242424243</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -1153,8 +1332,11 @@
       <c r="D38">
         <v>0.86363636363636365</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E38" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -1167,8 +1349,11 @@
       <c r="D39">
         <v>0.86363636363636365</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E39" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -1181,8 +1366,11 @@
       <c r="D40">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -1195,8 +1383,11 @@
       <c r="D41">
         <v>0.74242424242424243</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -1209,8 +1400,11 @@
       <c r="D42">
         <v>0.62121212121212122</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E42" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -1223,8 +1417,11 @@
       <c r="D43">
         <v>0.65151515151515149</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E43" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -1237,8 +1434,11 @@
       <c r="D44">
         <v>0.43939393939393928</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -1251,8 +1451,11 @@
       <c r="D45">
         <v>0.43939393939393928</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E45" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -1265,8 +1468,11 @@
       <c r="D46">
         <v>0.60606060606060597</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -1279,8 +1485,11 @@
       <c r="D47">
         <v>0.68181818181818188</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E47" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -1293,8 +1502,11 @@
       <c r="D48">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E48" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -1307,8 +1519,11 @@
       <c r="D49">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -1321,8 +1536,11 @@
       <c r="D50">
         <v>0.72727272727272729</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E50" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -1335,8 +1553,11 @@
       <c r="D51">
         <v>0.74242424242424243</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E51" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -1349,8 +1570,11 @@
       <c r="D52">
         <v>0.43939393939393928</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -1363,8 +1587,11 @@
       <c r="D53">
         <v>0.56060606060606055</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E53" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -1377,8 +1604,11 @@
       <c r="D54">
         <v>0.53030303030303028</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E54" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -1391,8 +1621,11 @@
       <c r="D55">
         <v>0.83333333333333326</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E55" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -1405,8 +1638,11 @@
       <c r="D56">
         <v>0.60606060606060597</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E56" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -1419,8 +1655,11 @@
       <c r="D57">
         <v>0.27272727272727271</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E57" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -1433,8 +1672,11 @@
       <c r="D58">
         <v>0.60606060606060597</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E58" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -1447,8 +1689,11 @@
       <c r="D59">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E59" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -1461,8 +1706,11 @@
       <c r="D60">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E60" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -1475,8 +1723,11 @@
       <c r="D61">
         <v>0.77272727272727271</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E61" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -1489,8 +1740,11 @@
       <c r="D62">
         <v>0.48484848484848492</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E62" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>8</v>
       </c>
@@ -1503,8 +1757,11 @@
       <c r="D63">
         <v>0.53030303030303028</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -1517,8 +1774,11 @@
       <c r="D64">
         <v>0.40909090909090912</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E64" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -1531,8 +1791,11 @@
       <c r="D65">
         <v>0.65151515151515149</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E65" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>8</v>
       </c>
@@ -1545,8 +1808,11 @@
       <c r="D66">
         <v>0.60606060606060597</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E66" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -1559,8 +1825,11 @@
       <c r="D67">
         <v>0.40909090909090912</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E67" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -1573,8 +1842,11 @@
       <c r="D68">
         <v>0.36363636363636359</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E68" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -1587,8 +1859,11 @@
       <c r="D69">
         <v>0.65151515151515149</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E69" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -1601,8 +1876,11 @@
       <c r="D70">
         <v>0.62121212121212122</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E70" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -1615,8 +1893,11 @@
       <c r="D71">
         <v>0.53030303030303028</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E71" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>8</v>
       </c>
@@ -1629,8 +1910,11 @@
       <c r="D72">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E72" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>8</v>
       </c>
@@ -1643,8 +1927,11 @@
       <c r="D73">
         <v>0.43939393939393928</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E73" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -1657,8 +1944,11 @@
       <c r="D74">
         <v>0.45454545454545447</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E74" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -1671,8 +1961,11 @@
       <c r="D75">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E75" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -1685,8 +1978,11 @@
       <c r="D76">
         <v>0.48484848484848492</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E76" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -1699,8 +1995,11 @@
       <c r="D77">
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E77" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -1713,8 +2012,11 @@
       <c r="D78">
         <v>0.74242424242424243</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E78" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -1727,8 +2029,11 @@
       <c r="D79">
         <v>0.60606060606060597</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E79" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -1741,8 +2046,11 @@
       <c r="D80">
         <v>0.74242424242424243</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E80" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -1755,8 +2063,11 @@
       <c r="D81">
         <v>0.40909090909090912</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E81" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -1769,8 +2080,11 @@
       <c r="D82">
         <v>0.39393939393939392</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E82" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -1783,8 +2097,11 @@
       <c r="D83">
         <v>0.74242424242424243</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E83" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -1797,8 +2114,11 @@
       <c r="D84">
         <v>0.53030303030303028</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E84" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -1811,8 +2131,11 @@
       <c r="D85">
         <v>0.62121212121212122</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E85" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -1825,8 +2148,11 @@
       <c r="D86">
         <v>0.27272727272727271</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E86" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>8</v>
       </c>
@@ -1839,8 +2165,11 @@
       <c r="D87">
         <v>0.74242424242424243</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E87" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -1853,8 +2182,11 @@
       <c r="D88">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E88" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>8</v>
       </c>
@@ -1867,8 +2199,11 @@
       <c r="D89">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E89" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>8</v>
       </c>
@@ -1881,8 +2216,11 @@
       <c r="D90">
         <v>0.62121212121212122</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E90" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>8</v>
       </c>
@@ -1895,8 +2233,11 @@
       <c r="D91">
         <v>0.56060606060606055</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E91" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -1909,8 +2250,11 @@
       <c r="D92">
         <v>0.62121212121212122</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E92" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -1923,8 +2267,11 @@
       <c r="D93">
         <v>0.31818181818181818</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E93" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -1937,8 +2284,11 @@
       <c r="D94">
         <v>0.31818181818181818</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E94" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -1951,8 +2301,11 @@
       <c r="D95">
         <v>0.43939393939393928</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E95" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>8</v>
       </c>
@@ -1965,8 +2318,11 @@
       <c r="D96">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E96" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -1979,8 +2335,11 @@
       <c r="D97">
         <v>0.65151515151515149</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E97" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -1993,8 +2352,11 @@
       <c r="D98">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E98" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -2007,8 +2369,11 @@
       <c r="D99">
         <v>0.53030303030303028</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E99" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -2021,8 +2386,11 @@
       <c r="D100">
         <v>0.56060606060606055</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E100" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -2035,8 +2403,11 @@
       <c r="D101">
         <v>0.65151515151515149</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E101" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -2049,8 +2420,11 @@
       <c r="D102">
         <v>0.48484848484848492</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E102" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -2063,8 +2437,11 @@
       <c r="D103">
         <v>0.51515151515151514</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E103" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -2077,8 +2454,11 @@
       <c r="D104">
         <v>0.56060606060606055</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E104" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -2091,8 +2471,11 @@
       <c r="D105">
         <v>0.60606060606060597</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E105" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -2105,8 +2488,11 @@
       <c r="D106">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E106" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -2119,8 +2505,11 @@
       <c r="D107">
         <v>0.53030303030303028</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E107" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -2133,8 +2522,11 @@
       <c r="D108">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E108" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>40</v>
       </c>
@@ -2147,8 +2539,11 @@
       <c r="D109">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E109" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>40</v>
       </c>
@@ -2161,8 +2556,11 @@
       <c r="D110">
         <v>0.53030303030303028</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E110" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>40</v>
       </c>
@@ -2175,8 +2573,11 @@
       <c r="D111">
         <v>0.59090909090909094</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E111" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>40</v>
       </c>
@@ -2189,8 +2590,11 @@
       <c r="D112">
         <v>0.43939393939393928</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E112" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -2203,8 +2607,11 @@
       <c r="D113">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E113" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>40</v>
       </c>
@@ -2217,8 +2624,11 @@
       <c r="D114">
         <v>0.48484848484848492</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E114" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>40</v>
       </c>
@@ -2231,8 +2641,11 @@
       <c r="D115">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E115" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>40</v>
       </c>
@@ -2245,8 +2658,11 @@
       <c r="D116">
         <v>0.43939393939393928</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E116" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>40</v>
       </c>
@@ -2259,8 +2675,11 @@
       <c r="D117">
         <v>0.31818181818181818</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E117" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>40</v>
       </c>
@@ -2273,8 +2692,11 @@
       <c r="D118">
         <v>0.31818181818181818</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E118" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>40</v>
       </c>
@@ -2287,8 +2709,11 @@
       <c r="D119">
         <v>0.65151515151515149</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E119" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>40</v>
       </c>
@@ -2301,8 +2726,11 @@
       <c r="D120">
         <v>0.69696969696969702</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E120" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>40</v>
       </c>
@@ -2315,8 +2743,11 @@
       <c r="D121">
         <v>0.43939393939393928</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E121" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>40</v>
       </c>
@@ -2329,8 +2760,11 @@
       <c r="D122">
         <v>0.62121212121212122</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E122" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>40</v>
       </c>
@@ -2343,8 +2777,11 @@
       <c r="D123">
         <v>0.60606060606060597</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E123" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>40</v>
       </c>
@@ -2357,8 +2794,11 @@
       <c r="D124">
         <v>0.22727272727272729</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E124" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>40</v>
       </c>
@@ -2371,8 +2811,11 @@
       <c r="D125">
         <v>0.45454545454545447</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E125" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>40</v>
       </c>
@@ -2385,8 +2828,11 @@
       <c r="D126">
         <v>0.60606060606060597</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E126" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>40</v>
       </c>
@@ -2399,8 +2845,11 @@
       <c r="D127">
         <v>0.45454545454545447</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E127" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>40</v>
       </c>
@@ -2413,8 +2862,11 @@
       <c r="D128">
         <v>0.78787878787878785</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E128" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>40</v>
       </c>
@@ -2427,8 +2879,11 @@
       <c r="D129">
         <v>0.65151515151515149</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E129" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>40</v>
       </c>
@@ -2441,8 +2896,11 @@
       <c r="D130">
         <v>0.5757575757575758</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E130" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>40</v>
       </c>
@@ -2455,8 +2913,11 @@
       <c r="D131">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E131" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>40</v>
       </c>
@@ -2469,8 +2930,11 @@
       <c r="D132">
         <v>0.2121212121212121</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E132" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>40</v>
       </c>
@@ -2483,8 +2947,11 @@
       <c r="D133">
         <v>0.48484848484848492</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E133" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>40</v>
       </c>
@@ -2497,8 +2964,11 @@
       <c r="D134">
         <v>0.53030303030303028</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E134" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>40</v>
       </c>
@@ -2511,8 +2981,11 @@
       <c r="D135">
         <v>0.53030303030303028</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E135" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>40</v>
       </c>
@@ -2525,8 +2998,11 @@
       <c r="D136">
         <v>0.43939393939393928</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E136" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>40</v>
       </c>
@@ -2539,8 +3015,11 @@
       <c r="D137">
         <v>0.74242424242424243</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E137" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>40</v>
       </c>
@@ -2553,8 +3032,11 @@
       <c r="D138">
         <v>0.78787878787878785</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E138" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>40</v>
       </c>
@@ -2567,8 +3049,11 @@
       <c r="D139">
         <v>0.39393939393939392</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E139" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>40</v>
       </c>
@@ -2581,8 +3066,11 @@
       <c r="D140">
         <v>0.60606060606060597</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E140" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>40</v>
       </c>
@@ -2595,8 +3083,11 @@
       <c r="D141">
         <v>0.43939393939393928</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E141" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>40</v>
       </c>
@@ -2609,8 +3100,11 @@
       <c r="D142">
         <v>0.62121212121212122</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E142" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>40</v>
       </c>
@@ -2623,8 +3117,11 @@
       <c r="D143">
         <v>0.27272727272727271</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E143" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>40</v>
       </c>
@@ -2637,8 +3134,11 @@
       <c r="D144">
         <v>0.56060606060606055</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E144" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>40</v>
       </c>
@@ -2651,8 +3151,11 @@
       <c r="D145">
         <v>0.48484848484848492</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E145" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>40</v>
       </c>
@@ -2665,8 +3168,11 @@
       <c r="D146">
         <v>0.53030303030303028</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E146" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>40</v>
       </c>
@@ -2679,8 +3185,11 @@
       <c r="D147">
         <v>0.65151515151515149</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E147" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>40</v>
       </c>
@@ -2693,8 +3202,11 @@
       <c r="D148">
         <v>0.45454545454545447</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E148" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>40</v>
       </c>
@@ -2707,8 +3219,11 @@
       <c r="D149">
         <v>0.53030303030303028</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E149" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>40</v>
       </c>
@@ -2721,8 +3236,11 @@
       <c r="D150">
         <v>0.56060606060606055</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E150" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>40</v>
       </c>
@@ -2734,6 +3252,2559 @@
       </c>
       <c r="D151">
         <v>0.39393939393939392</v>
+      </c>
+      <c r="E151" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>4</v>
+      </c>
+      <c r="B152" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152">
+        <v>0.57658730158730165</v>
+      </c>
+      <c r="D152">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E152" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>4</v>
+      </c>
+      <c r="B153" t="s">
+        <v>5</v>
+      </c>
+      <c r="C153">
+        <v>0.61746031746031749</v>
+      </c>
+      <c r="D153">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E153" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>4</v>
+      </c>
+      <c r="B154" t="s">
+        <v>5</v>
+      </c>
+      <c r="C154">
+        <v>0.73769841269841263</v>
+      </c>
+      <c r="D154">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E154" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>4</v>
+      </c>
+      <c r="B155" t="s">
+        <v>5</v>
+      </c>
+      <c r="C155">
+        <v>0.61666666666666659</v>
+      </c>
+      <c r="D155">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E155" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>4</v>
+      </c>
+      <c r="B156" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156">
+        <v>0.62023809523809526</v>
+      </c>
+      <c r="D156">
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="E156" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>4</v>
+      </c>
+      <c r="B157" t="s">
+        <v>5</v>
+      </c>
+      <c r="C157">
+        <v>0.60992063492063486</v>
+      </c>
+      <c r="D157">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E157" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>4</v>
+      </c>
+      <c r="B158" t="s">
+        <v>5</v>
+      </c>
+      <c r="C158">
+        <v>0.61666666666666659</v>
+      </c>
+      <c r="D158">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E158" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>4</v>
+      </c>
+      <c r="B159" t="s">
+        <v>5</v>
+      </c>
+      <c r="C159">
+        <v>0.57261904761904758</v>
+      </c>
+      <c r="D159">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E159" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>4</v>
+      </c>
+      <c r="B160" t="s">
+        <v>5</v>
+      </c>
+      <c r="C160">
+        <v>0.6884920634920636</v>
+      </c>
+      <c r="D160">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E160" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>4</v>
+      </c>
+      <c r="B161" t="s">
+        <v>5</v>
+      </c>
+      <c r="C161">
+        <v>0.70952380952380956</v>
+      </c>
+      <c r="D161">
+        <v>0.46969696969696972</v>
+      </c>
+      <c r="E161" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>4</v>
+      </c>
+      <c r="B162" t="s">
+        <v>72</v>
+      </c>
+      <c r="C162">
+        <v>0.5</v>
+      </c>
+      <c r="D162">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="E162" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>4</v>
+      </c>
+      <c r="B163" t="s">
+        <v>5</v>
+      </c>
+      <c r="C163">
+        <v>0.59523809523809523</v>
+      </c>
+      <c r="D163">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E163" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>4</v>
+      </c>
+      <c r="B164" t="s">
+        <v>5</v>
+      </c>
+      <c r="C164">
+        <v>0.50595238095238093</v>
+      </c>
+      <c r="D164">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="E164" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>4</v>
+      </c>
+      <c r="B165" t="s">
+        <v>5</v>
+      </c>
+      <c r="C165">
+        <v>0.69841269841269848</v>
+      </c>
+      <c r="D165">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E165" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>4</v>
+      </c>
+      <c r="B166" t="s">
+        <v>5</v>
+      </c>
+      <c r="C166">
+        <v>0.50357142857142856</v>
+      </c>
+      <c r="D166">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E166" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>4</v>
+      </c>
+      <c r="B167" t="s">
+        <v>5</v>
+      </c>
+      <c r="C167">
+        <v>0.60515873015873012</v>
+      </c>
+      <c r="D167">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E167" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>4</v>
+      </c>
+      <c r="B168" t="s">
+        <v>5</v>
+      </c>
+      <c r="C168">
+        <v>0.73492063492063497</v>
+      </c>
+      <c r="D168">
+        <v>0.43939393939393928</v>
+      </c>
+      <c r="E168" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>4</v>
+      </c>
+      <c r="B169" t="s">
+        <v>5</v>
+      </c>
+      <c r="C169">
+        <v>0.63769841269841276</v>
+      </c>
+      <c r="D169">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E169" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>4</v>
+      </c>
+      <c r="B170" t="s">
+        <v>5</v>
+      </c>
+      <c r="C170">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="D170">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E170" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>4</v>
+      </c>
+      <c r="B171" t="s">
+        <v>5</v>
+      </c>
+      <c r="C171">
+        <v>0.62777777777777777</v>
+      </c>
+      <c r="D171">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E171" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>4</v>
+      </c>
+      <c r="B172" t="s">
+        <v>5</v>
+      </c>
+      <c r="C172">
+        <v>0.52142857142857146</v>
+      </c>
+      <c r="D172">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E172" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>4</v>
+      </c>
+      <c r="B173" t="s">
+        <v>5</v>
+      </c>
+      <c r="C173">
+        <v>0.61666666666666659</v>
+      </c>
+      <c r="D173">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E173" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>4</v>
+      </c>
+      <c r="B174" t="s">
+        <v>5</v>
+      </c>
+      <c r="C174">
+        <v>0.5896825396825397</v>
+      </c>
+      <c r="D174">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E174" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>4</v>
+      </c>
+      <c r="B175" t="s">
+        <v>5</v>
+      </c>
+      <c r="C175">
+        <v>0.65992063492063491</v>
+      </c>
+      <c r="D175">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E175" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>4</v>
+      </c>
+      <c r="B176" t="s">
+        <v>5</v>
+      </c>
+      <c r="C176">
+        <v>0.73333333333333339</v>
+      </c>
+      <c r="D176">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E176" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>4</v>
+      </c>
+      <c r="B177" t="s">
+        <v>5</v>
+      </c>
+      <c r="C177">
+        <v>0.57817460317460323</v>
+      </c>
+      <c r="D177">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E177" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>4</v>
+      </c>
+      <c r="B178" t="s">
+        <v>7</v>
+      </c>
+      <c r="C178">
+        <v>0.5</v>
+      </c>
+      <c r="D178">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E178" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>4</v>
+      </c>
+      <c r="B179" t="s">
+        <v>6</v>
+      </c>
+      <c r="C179">
+        <v>0.58888888888888891</v>
+      </c>
+      <c r="D179">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E179" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>4</v>
+      </c>
+      <c r="B180" t="s">
+        <v>5</v>
+      </c>
+      <c r="C180">
+        <v>0.55952380952380965</v>
+      </c>
+      <c r="D180">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E180" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>4</v>
+      </c>
+      <c r="B181" t="s">
+        <v>5</v>
+      </c>
+      <c r="C181">
+        <v>0.66547619047619044</v>
+      </c>
+      <c r="D181">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E181" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>4</v>
+      </c>
+      <c r="B182" t="s">
+        <v>5</v>
+      </c>
+      <c r="C182">
+        <v>0.62261904761904763</v>
+      </c>
+      <c r="D182">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E182" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>4</v>
+      </c>
+      <c r="B183" t="s">
+        <v>5</v>
+      </c>
+      <c r="C183">
+        <v>0.59603174603174602</v>
+      </c>
+      <c r="D183">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E183" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>4</v>
+      </c>
+      <c r="B184" t="s">
+        <v>5</v>
+      </c>
+      <c r="C184">
+        <v>0.57817460317460323</v>
+      </c>
+      <c r="D184">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E184" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>4</v>
+      </c>
+      <c r="B185" t="s">
+        <v>5</v>
+      </c>
+      <c r="C185">
+        <v>0.66746031746031742</v>
+      </c>
+      <c r="D185">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E185" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>4</v>
+      </c>
+      <c r="B186" t="s">
+        <v>5</v>
+      </c>
+      <c r="C186">
+        <v>0.71388888888888891</v>
+      </c>
+      <c r="D186">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E186" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>4</v>
+      </c>
+      <c r="B187" t="s">
+        <v>5</v>
+      </c>
+      <c r="C187">
+        <v>0.56388888888888888</v>
+      </c>
+      <c r="D187">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E187" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>4</v>
+      </c>
+      <c r="B188" t="s">
+        <v>5</v>
+      </c>
+      <c r="C188">
+        <v>0.63134920634920633</v>
+      </c>
+      <c r="D188">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E188" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>4</v>
+      </c>
+      <c r="B189" t="s">
+        <v>5</v>
+      </c>
+      <c r="C189">
+        <v>0.59206349206349207</v>
+      </c>
+      <c r="D189">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E189" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>4</v>
+      </c>
+      <c r="B190" t="s">
+        <v>5</v>
+      </c>
+      <c r="C190">
+        <v>0.71666666666666679</v>
+      </c>
+      <c r="D190">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="E190" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>4</v>
+      </c>
+      <c r="B191" t="s">
+        <v>5</v>
+      </c>
+      <c r="C191">
+        <v>0.61428571428571421</v>
+      </c>
+      <c r="D191">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E191" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>4</v>
+      </c>
+      <c r="B192" t="s">
+        <v>5</v>
+      </c>
+      <c r="C192">
+        <v>0.56904761904761914</v>
+      </c>
+      <c r="D192">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E192" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>4</v>
+      </c>
+      <c r="B193" t="s">
+        <v>5</v>
+      </c>
+      <c r="C193">
+        <v>0.66349206349206347</v>
+      </c>
+      <c r="D193">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E193" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>4</v>
+      </c>
+      <c r="B194" t="s">
+        <v>5</v>
+      </c>
+      <c r="C194">
+        <v>0.67380952380952375</v>
+      </c>
+      <c r="D194">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E194" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>4</v>
+      </c>
+      <c r="B195" t="s">
+        <v>5</v>
+      </c>
+      <c r="C195">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="D195">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="E195" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>4</v>
+      </c>
+      <c r="B196" t="s">
+        <v>5</v>
+      </c>
+      <c r="C196">
+        <v>0.60992063492063497</v>
+      </c>
+      <c r="D196">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E196" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>4</v>
+      </c>
+      <c r="B197" t="s">
+        <v>5</v>
+      </c>
+      <c r="C197">
+        <v>0.56984126984126982</v>
+      </c>
+      <c r="D197">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E197" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>4</v>
+      </c>
+      <c r="B198" t="s">
+        <v>5</v>
+      </c>
+      <c r="C198">
+        <v>0.7146825396825397</v>
+      </c>
+      <c r="D198">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E198" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>4</v>
+      </c>
+      <c r="B199" t="s">
+        <v>5</v>
+      </c>
+      <c r="C199">
+        <v>0.55119047619047612</v>
+      </c>
+      <c r="D199">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E199" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>4</v>
+      </c>
+      <c r="B200" t="s">
+        <v>5</v>
+      </c>
+      <c r="C200">
+        <v>0.66785714285714282</v>
+      </c>
+      <c r="D200">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E200" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>4</v>
+      </c>
+      <c r="B201" t="s">
+        <v>5</v>
+      </c>
+      <c r="C201">
+        <v>0.598015873015873</v>
+      </c>
+      <c r="D201">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E201" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>8</v>
+      </c>
+      <c r="B202" t="s">
+        <v>32</v>
+      </c>
+      <c r="C202">
+        <v>0.65238095238095239</v>
+      </c>
+      <c r="D202">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E202" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>8</v>
+      </c>
+      <c r="B203" t="s">
+        <v>17</v>
+      </c>
+      <c r="C203">
+        <v>0.65753968253968254</v>
+      </c>
+      <c r="D203">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E203" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>8</v>
+      </c>
+      <c r="B204" t="s">
+        <v>30</v>
+      </c>
+      <c r="C204">
+        <v>0.70674603174603179</v>
+      </c>
+      <c r="D204">
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="E204" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>8</v>
+      </c>
+      <c r="B205" t="s">
+        <v>19</v>
+      </c>
+      <c r="C205">
+        <v>0.62301587301587302</v>
+      </c>
+      <c r="D205">
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="E205" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>8</v>
+      </c>
+      <c r="B206" t="s">
+        <v>73</v>
+      </c>
+      <c r="C206">
+        <v>0.71309523809523812</v>
+      </c>
+      <c r="D206">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="E206" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>8</v>
+      </c>
+      <c r="B207" t="s">
+        <v>19</v>
+      </c>
+      <c r="C207">
+        <v>0.62380952380952381</v>
+      </c>
+      <c r="D207">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E207" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>8</v>
+      </c>
+      <c r="B208" t="s">
+        <v>20</v>
+      </c>
+      <c r="C208">
+        <v>0.70436507936507942</v>
+      </c>
+      <c r="D208">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E208" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>8</v>
+      </c>
+      <c r="B209" t="s">
+        <v>13</v>
+      </c>
+      <c r="C209">
+        <v>0.68928571428571439</v>
+      </c>
+      <c r="D209">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E209" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>8</v>
+      </c>
+      <c r="B210" t="s">
+        <v>27</v>
+      </c>
+      <c r="C210">
+        <v>0.66309523809523807</v>
+      </c>
+      <c r="D210">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E210" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>8</v>
+      </c>
+      <c r="B211" t="s">
+        <v>74</v>
+      </c>
+      <c r="C211">
+        <v>0.78452380952380951</v>
+      </c>
+      <c r="D211">
+        <v>0.46969696969696972</v>
+      </c>
+      <c r="E211" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>8</v>
+      </c>
+      <c r="B212" t="s">
+        <v>13</v>
+      </c>
+      <c r="C212">
+        <v>0.55595238095238086</v>
+      </c>
+      <c r="D212">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E212" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>8</v>
+      </c>
+      <c r="B213" t="s">
+        <v>10</v>
+      </c>
+      <c r="C213">
+        <v>0.72103174603174602</v>
+      </c>
+      <c r="D213">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E213" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>8</v>
+      </c>
+      <c r="B214" t="s">
+        <v>32</v>
+      </c>
+      <c r="C214">
+        <v>0.62261904761904763</v>
+      </c>
+      <c r="D214">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E214" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>8</v>
+      </c>
+      <c r="B215" t="s">
+        <v>36</v>
+      </c>
+      <c r="C215">
+        <v>0.67619047619047612</v>
+      </c>
+      <c r="D215">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E215" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>8</v>
+      </c>
+      <c r="B216" t="s">
+        <v>10</v>
+      </c>
+      <c r="C216">
+        <v>0.6432539682539683</v>
+      </c>
+      <c r="D216">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E216" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>8</v>
+      </c>
+      <c r="B217" t="s">
+        <v>32</v>
+      </c>
+      <c r="C217">
+        <v>0.70396825396825402</v>
+      </c>
+      <c r="D217">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E217" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>8</v>
+      </c>
+      <c r="B218" t="s">
+        <v>21</v>
+      </c>
+      <c r="C218">
+        <v>0.69603174603174611</v>
+      </c>
+      <c r="D218">
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="E218" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>8</v>
+      </c>
+      <c r="B219" t="s">
+        <v>75</v>
+      </c>
+      <c r="C219">
+        <v>0.66150793650793649</v>
+      </c>
+      <c r="D219">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E219" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>8</v>
+      </c>
+      <c r="B220" t="s">
+        <v>75</v>
+      </c>
+      <c r="C220">
+        <v>0.607936507936508</v>
+      </c>
+      <c r="D220">
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="E220" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>8</v>
+      </c>
+      <c r="B221" t="s">
+        <v>76</v>
+      </c>
+      <c r="C221">
+        <v>0.67658730158730152</v>
+      </c>
+      <c r="D221">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E221" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>8</v>
+      </c>
+      <c r="B222" t="s">
+        <v>77</v>
+      </c>
+      <c r="C222">
+        <v>0.51984126984126988</v>
+      </c>
+      <c r="D222">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E222" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>8</v>
+      </c>
+      <c r="B223" t="s">
+        <v>32</v>
+      </c>
+      <c r="C223">
+        <v>0.59523809523809523</v>
+      </c>
+      <c r="D223">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E223" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>8</v>
+      </c>
+      <c r="B224" t="s">
+        <v>78</v>
+      </c>
+      <c r="C224">
+        <v>0.63650793650793647</v>
+      </c>
+      <c r="D224">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E224" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>8</v>
+      </c>
+      <c r="B225" t="s">
+        <v>79</v>
+      </c>
+      <c r="C225">
+        <v>0.57896825396825402</v>
+      </c>
+      <c r="D225">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E225" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>8</v>
+      </c>
+      <c r="B226" t="s">
+        <v>27</v>
+      </c>
+      <c r="C226">
+        <v>0.72976190476190472</v>
+      </c>
+      <c r="D226">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E226" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>8</v>
+      </c>
+      <c r="B227" t="s">
+        <v>21</v>
+      </c>
+      <c r="C227">
+        <v>0.68214285714285727</v>
+      </c>
+      <c r="D227">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E227" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>8</v>
+      </c>
+      <c r="B228" t="s">
+        <v>34</v>
+      </c>
+      <c r="C228">
+        <v>0.56468253968253979</v>
+      </c>
+      <c r="D228">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E228" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>8</v>
+      </c>
+      <c r="B229" t="s">
+        <v>20</v>
+      </c>
+      <c r="C229">
+        <v>0.70793650793650797</v>
+      </c>
+      <c r="D229">
+        <v>0.43939393939393928</v>
+      </c>
+      <c r="E229" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>8</v>
+      </c>
+      <c r="B230" t="s">
+        <v>36</v>
+      </c>
+      <c r="C230">
+        <v>0.67896825396825411</v>
+      </c>
+      <c r="D230">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E230" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>8</v>
+      </c>
+      <c r="B231" t="s">
+        <v>21</v>
+      </c>
+      <c r="C231">
+        <v>0.59285714285714286</v>
+      </c>
+      <c r="D231">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E231" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>8</v>
+      </c>
+      <c r="B232" t="s">
+        <v>20</v>
+      </c>
+      <c r="C232">
+        <v>0.62777777777777777</v>
+      </c>
+      <c r="D232">
+        <v>0.68181818181818188</v>
+      </c>
+      <c r="E232" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>8</v>
+      </c>
+      <c r="B233" t="s">
+        <v>32</v>
+      </c>
+      <c r="C233">
+        <v>0.63531746031746028</v>
+      </c>
+      <c r="D233">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E233" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>8</v>
+      </c>
+      <c r="B234" t="s">
+        <v>37</v>
+      </c>
+      <c r="C234">
+        <v>0.55952380952380953</v>
+      </c>
+      <c r="D234">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E234" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>8</v>
+      </c>
+      <c r="B235" t="s">
+        <v>14</v>
+      </c>
+      <c r="C235">
+        <v>0.65873015873015872</v>
+      </c>
+      <c r="D235">
+        <v>0.43939393939393928</v>
+      </c>
+      <c r="E235" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>8</v>
+      </c>
+      <c r="B236" t="s">
+        <v>36</v>
+      </c>
+      <c r="C236">
+        <v>0.62936507936507935</v>
+      </c>
+      <c r="D236">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E236" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>8</v>
+      </c>
+      <c r="B237" t="s">
+        <v>27</v>
+      </c>
+      <c r="C237">
+        <v>0.75238095238095237</v>
+      </c>
+      <c r="D237">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E237" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>8</v>
+      </c>
+      <c r="B238" t="s">
+        <v>21</v>
+      </c>
+      <c r="C238">
+        <v>0.70873015873015877</v>
+      </c>
+      <c r="D238">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E238" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>8</v>
+      </c>
+      <c r="B239" t="s">
+        <v>32</v>
+      </c>
+      <c r="C239">
+        <v>0.74285714285714288</v>
+      </c>
+      <c r="D239">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E239" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>8</v>
+      </c>
+      <c r="B240" t="s">
+        <v>34</v>
+      </c>
+      <c r="C240">
+        <v>0.74206349206349209</v>
+      </c>
+      <c r="D240">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E240" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>8</v>
+      </c>
+      <c r="B241" t="s">
+        <v>80</v>
+      </c>
+      <c r="C241">
+        <v>0.57500000000000007</v>
+      </c>
+      <c r="D241">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="E241" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>8</v>
+      </c>
+      <c r="B242" t="s">
+        <v>81</v>
+      </c>
+      <c r="C242">
+        <v>0.62777777777777777</v>
+      </c>
+      <c r="D242">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E242" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>8</v>
+      </c>
+      <c r="B243" t="s">
+        <v>10</v>
+      </c>
+      <c r="C243">
+        <v>0.78253968253968254</v>
+      </c>
+      <c r="D243">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E243" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>8</v>
+      </c>
+      <c r="B244" t="s">
+        <v>31</v>
+      </c>
+      <c r="C244">
+        <v>0.71507936507936509</v>
+      </c>
+      <c r="D244">
+        <v>0.43939393939393928</v>
+      </c>
+      <c r="E244" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>8</v>
+      </c>
+      <c r="B245" t="s">
+        <v>36</v>
+      </c>
+      <c r="C245">
+        <v>0.7503968253968254</v>
+      </c>
+      <c r="D245">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E245" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>8</v>
+      </c>
+      <c r="B246" t="s">
+        <v>32</v>
+      </c>
+      <c r="C246">
+        <v>0.68928571428571439</v>
+      </c>
+      <c r="D246">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E246" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>8</v>
+      </c>
+      <c r="B247" t="s">
+        <v>75</v>
+      </c>
+      <c r="C247">
+        <v>0.57142857142857151</v>
+      </c>
+      <c r="D247">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E247" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>8</v>
+      </c>
+      <c r="B248" t="s">
+        <v>29</v>
+      </c>
+      <c r="C248">
+        <v>0.71785714285714286</v>
+      </c>
+      <c r="D248">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E248" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>8</v>
+      </c>
+      <c r="B249" t="s">
+        <v>82</v>
+      </c>
+      <c r="C249">
+        <v>0.67539682539682533</v>
+      </c>
+      <c r="D249">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E249" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>8</v>
+      </c>
+      <c r="B250" t="s">
+        <v>34</v>
+      </c>
+      <c r="C250">
+        <v>0.59087301587301588</v>
+      </c>
+      <c r="D250">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E250" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>8</v>
+      </c>
+      <c r="B251" t="s">
+        <v>9</v>
+      </c>
+      <c r="C251">
+        <v>0.63849206349206356</v>
+      </c>
+      <c r="D251">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E251" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>40</v>
+      </c>
+      <c r="B252" t="s">
+        <v>83</v>
+      </c>
+      <c r="C252">
+        <v>0.5527777777777777</v>
+      </c>
+      <c r="D252">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E252" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>40</v>
+      </c>
+      <c r="B253" t="s">
+        <v>71</v>
+      </c>
+      <c r="C253">
+        <v>0.73452380952380958</v>
+      </c>
+      <c r="D253">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E253" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>40</v>
+      </c>
+      <c r="B254" t="s">
+        <v>84</v>
+      </c>
+      <c r="C254">
+        <v>0.62936507936507935</v>
+      </c>
+      <c r="D254">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E254" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>40</v>
+      </c>
+      <c r="B255" t="s">
+        <v>84</v>
+      </c>
+      <c r="C255">
+        <v>0.7583333333333333</v>
+      </c>
+      <c r="D255">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E255" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>40</v>
+      </c>
+      <c r="B256" t="s">
+        <v>71</v>
+      </c>
+      <c r="C256">
+        <v>0.5896825396825397</v>
+      </c>
+      <c r="D256">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E256" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>40</v>
+      </c>
+      <c r="B257" t="s">
+        <v>42</v>
+      </c>
+      <c r="C257">
+        <v>0.67301587301587296</v>
+      </c>
+      <c r="D257">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E257" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>40</v>
+      </c>
+      <c r="B258" t="s">
+        <v>85</v>
+      </c>
+      <c r="C258">
+        <v>0.61071428571428577</v>
+      </c>
+      <c r="D258">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E258" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>40</v>
+      </c>
+      <c r="B259" t="s">
+        <v>46</v>
+      </c>
+      <c r="C259">
+        <v>0.62698412698412687</v>
+      </c>
+      <c r="D259">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E259" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>40</v>
+      </c>
+      <c r="B260" t="s">
+        <v>50</v>
+      </c>
+      <c r="C260">
+        <v>0.73531746031746037</v>
+      </c>
+      <c r="D260">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E260" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>40</v>
+      </c>
+      <c r="B261" t="s">
+        <v>86</v>
+      </c>
+      <c r="C261">
+        <v>0.76825396825396819</v>
+      </c>
+      <c r="D261">
+        <v>0.37878787878787878</v>
+      </c>
+      <c r="E261" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>40</v>
+      </c>
+      <c r="B262" t="s">
+        <v>87</v>
+      </c>
+      <c r="C262">
+        <v>0.6337301587301587</v>
+      </c>
+      <c r="D262">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E262" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>40</v>
+      </c>
+      <c r="B263" t="s">
+        <v>88</v>
+      </c>
+      <c r="C263">
+        <v>0.67658730158730152</v>
+      </c>
+      <c r="D263">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E263" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>40</v>
+      </c>
+      <c r="B264" t="s">
+        <v>88</v>
+      </c>
+      <c r="C264">
+        <v>0.71785714285714286</v>
+      </c>
+      <c r="D264">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E264" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>40</v>
+      </c>
+      <c r="B265" t="s">
+        <v>59</v>
+      </c>
+      <c r="C265">
+        <v>0.73571428571428577</v>
+      </c>
+      <c r="D265">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E265" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>40</v>
+      </c>
+      <c r="B266" t="s">
+        <v>49</v>
+      </c>
+      <c r="C266">
+        <v>0.63611111111111118</v>
+      </c>
+      <c r="D266">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E266" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>40</v>
+      </c>
+      <c r="B267" t="s">
+        <v>50</v>
+      </c>
+      <c r="C267">
+        <v>0.54722222222222217</v>
+      </c>
+      <c r="D267">
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="E267" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>40</v>
+      </c>
+      <c r="B268" t="s">
+        <v>52</v>
+      </c>
+      <c r="C268">
+        <v>0.71388888888888891</v>
+      </c>
+      <c r="D268">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E268" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>40</v>
+      </c>
+      <c r="B269" t="s">
+        <v>68</v>
+      </c>
+      <c r="C269">
+        <v>0.74523809523809526</v>
+      </c>
+      <c r="D269">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E269" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>40</v>
+      </c>
+      <c r="B270" t="s">
+        <v>43</v>
+      </c>
+      <c r="C270">
+        <v>0.57976190476190481</v>
+      </c>
+      <c r="D270">
+        <v>0.43939393939393928</v>
+      </c>
+      <c r="E270" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>40</v>
+      </c>
+      <c r="B271" t="s">
+        <v>46</v>
+      </c>
+      <c r="C271">
+        <v>0.73373015873015868</v>
+      </c>
+      <c r="D271">
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="E271" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>40</v>
+      </c>
+      <c r="B272" t="s">
+        <v>89</v>
+      </c>
+      <c r="C272">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D272">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E272" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>40</v>
+      </c>
+      <c r="B273" t="s">
+        <v>71</v>
+      </c>
+      <c r="C273">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="D273">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E273" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>40</v>
+      </c>
+      <c r="B274" t="s">
+        <v>54</v>
+      </c>
+      <c r="C274">
+        <v>0.76150793650793647</v>
+      </c>
+      <c r="D274">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E274" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>40</v>
+      </c>
+      <c r="B275" t="s">
+        <v>42</v>
+      </c>
+      <c r="C275">
+        <v>0.59166666666666667</v>
+      </c>
+      <c r="D275">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E275" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>40</v>
+      </c>
+      <c r="B276" t="s">
+        <v>90</v>
+      </c>
+      <c r="C276">
+        <v>0.73769841269841263</v>
+      </c>
+      <c r="D276">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E276" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>40</v>
+      </c>
+      <c r="B277" t="s">
+        <v>43</v>
+      </c>
+      <c r="C277">
+        <v>0.65317460317460319</v>
+      </c>
+      <c r="D277">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="E277" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>40</v>
+      </c>
+      <c r="B278" t="s">
+        <v>89</v>
+      </c>
+      <c r="C278">
+        <v>0.62261904761904763</v>
+      </c>
+      <c r="D278">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E278" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>40</v>
+      </c>
+      <c r="B279" t="s">
+        <v>59</v>
+      </c>
+      <c r="C279">
+        <v>0.69603174603174589</v>
+      </c>
+      <c r="D279">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E279" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>40</v>
+      </c>
+      <c r="B280" t="s">
+        <v>46</v>
+      </c>
+      <c r="C280">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="D280">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="E280" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>40</v>
+      </c>
+      <c r="B281" t="s">
+        <v>91</v>
+      </c>
+      <c r="C281">
+        <v>0.68373015873015885</v>
+      </c>
+      <c r="D281">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E281" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>40</v>
+      </c>
+      <c r="B282" t="s">
+        <v>68</v>
+      </c>
+      <c r="C282">
+        <v>0.70476190476190481</v>
+      </c>
+      <c r="D282">
+        <v>0.51515151515151514</v>
+      </c>
+      <c r="E282" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>40</v>
+      </c>
+      <c r="B283" t="s">
+        <v>57</v>
+      </c>
+      <c r="C283">
+        <v>0.66428571428571426</v>
+      </c>
+      <c r="D283">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E283" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>40</v>
+      </c>
+      <c r="B284" t="s">
+        <v>44</v>
+      </c>
+      <c r="C284">
+        <v>0.65039682539682542</v>
+      </c>
+      <c r="D284">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E284" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>40</v>
+      </c>
+      <c r="B285" t="s">
+        <v>85</v>
+      </c>
+      <c r="C285">
+        <v>0.70793650793650797</v>
+      </c>
+      <c r="D285">
+        <v>0.36363636363636359</v>
+      </c>
+      <c r="E285" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>40</v>
+      </c>
+      <c r="B286" t="s">
+        <v>43</v>
+      </c>
+      <c r="C286">
+        <v>0.63015873015873014</v>
+      </c>
+      <c r="D286">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E286" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>40</v>
+      </c>
+      <c r="B287" t="s">
+        <v>43</v>
+      </c>
+      <c r="C287">
+        <v>0.76269841269841276</v>
+      </c>
+      <c r="D287">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E287" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>40</v>
+      </c>
+      <c r="B288" t="s">
+        <v>48</v>
+      </c>
+      <c r="C288">
+        <v>0.68492063492063482</v>
+      </c>
+      <c r="D288">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E288" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>40</v>
+      </c>
+      <c r="B289" t="s">
+        <v>49</v>
+      </c>
+      <c r="C289">
+        <v>0.76825396825396819</v>
+      </c>
+      <c r="D289">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="E289" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>40</v>
+      </c>
+      <c r="B290" t="s">
+        <v>92</v>
+      </c>
+      <c r="C290">
+        <v>0.71071428571428574</v>
+      </c>
+      <c r="D290">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E290" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>40</v>
+      </c>
+      <c r="B291" t="s">
+        <v>41</v>
+      </c>
+      <c r="C291">
+        <v>0.70952380952380956</v>
+      </c>
+      <c r="D291">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E291" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>40</v>
+      </c>
+      <c r="B292" t="s">
+        <v>48</v>
+      </c>
+      <c r="C292">
+        <v>0.67301587301587296</v>
+      </c>
+      <c r="D292">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E292" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>40</v>
+      </c>
+      <c r="B293" t="s">
+        <v>57</v>
+      </c>
+      <c r="C293">
+        <v>0.73095238095238102</v>
+      </c>
+      <c r="D293">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E293" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>40</v>
+      </c>
+      <c r="B294" t="s">
+        <v>62</v>
+      </c>
+      <c r="C294">
+        <v>0.79960317460317454</v>
+      </c>
+      <c r="D294">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E294" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>40</v>
+      </c>
+      <c r="B295" t="s">
+        <v>93</v>
+      </c>
+      <c r="C295">
+        <v>0.78690476190476188</v>
+      </c>
+      <c r="D295">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E295" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>40</v>
+      </c>
+      <c r="B296" t="s">
+        <v>55</v>
+      </c>
+      <c r="C296">
+        <v>0.70714285714285718</v>
+      </c>
+      <c r="D296">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="E296" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>40</v>
+      </c>
+      <c r="B297" t="s">
+        <v>66</v>
+      </c>
+      <c r="C297">
+        <v>0.57063492063492072</v>
+      </c>
+      <c r="D297">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E297" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>40</v>
+      </c>
+      <c r="B298" t="s">
+        <v>51</v>
+      </c>
+      <c r="C298">
+        <v>0.71706349206349207</v>
+      </c>
+      <c r="D298">
+        <v>0.51515151515151514</v>
+      </c>
+      <c r="E298" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>40</v>
+      </c>
+      <c r="B299" t="s">
+        <v>61</v>
+      </c>
+      <c r="C299">
+        <v>0.68888888888888877</v>
+      </c>
+      <c r="D299">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E299" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>40</v>
+      </c>
+      <c r="B300" t="s">
+        <v>45</v>
+      </c>
+      <c r="C300">
+        <v>0.69603174603174589</v>
+      </c>
+      <c r="D300">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="E300" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>40</v>
+      </c>
+      <c r="B301" t="s">
+        <v>61</v>
+      </c>
+      <c r="C301">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="D301">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E301" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
